--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f13002e35d6260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II - General Motors Insurance</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0d12975625b7b9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
+          <t>https://www.indeed.com/viewjob?jk=e80f5516efca193f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
+          <t>https://www.indeed.com/viewjob?jk=0528c489587de6f9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea27190f32e93ae</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS ETL Data Engineer - HYBRID</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f3b0a20014410c8</t>
+          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Data Engineer II - General Motors Insurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
+          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
+          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AWS ETL Data Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f3b0a20014410c8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Architect - (ADLS, S3, or GCS).</t>
+          <t>Data Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066f34528bcf8419</t>
+          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Elasticsearch Experience</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863fe2721df72a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect - (ADLS, S3, or GCS).</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=066f34528bcf8419</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Engineer with Elasticsearch Experience</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,15 +1388,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
+          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Reliability Developer</t>
+          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Arctic Wolf Networks</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Software Backend Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb9a8bc7b5038ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>Senior Reliability Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Arctic Wolf Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ClosingLock</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior GCP CloudOps Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Azure Full Stack Developer</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb9a8bc7b5038ad</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
+          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Platform Architect, Strategy and Enablement</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SrinSoft Technologies</t>
+          <t>ClosingLock</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>US LBM AI Engineer</t>
+          <t>Senior GCP CloudOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
+          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer L3</t>
+          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Platform Architect, Strategy and Enablement</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
         </is>
       </c>
     </row>
@@ -2153,20 +2153,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SQL Server</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>SrinSoft Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Weston, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>US LBM AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer L3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
         </is>
       </c>
     </row>
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Professional Services)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c763a51fc327e6</t>
+          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Solutions Architect - Financial Services</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
+          <t>Solutions Architect - Financial Services (Professional Services)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
+          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,164 +3261,164 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
+          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cba82380663ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f66ed36e35c3928</t>
+          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09aaaaf6b05a7a81</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beeeb05481ffa3fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52126b35f95fb8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68a7d08fbe01d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,29 +3531,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2366d0095d71df3c</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f05b96a5cf11bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f555d911530273f0</t>
+          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77478365e47af5d</t>
+          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5e6e2b32efd5c0</t>
+          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf3af3715aea016</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cba82380663ee6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9962c699e7b6185</t>
+          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69a160c1457e1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64aa0159e9389e44</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2b960df7ed57e9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5d52259bf0471</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb3a4046ad04ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ce42688a381c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,1872 +3986,612 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>Lambda, Step Functions, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, Splunk, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f199052b0c23dcbd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9aec2a1b87419d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8913bab9f3417548</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32838dc534178bd3</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3e93739ca63bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a552782a87ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>eLinx Health, LLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b4a6ea360fcf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Middle Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Itransition</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>BigQuery, Snowflake, Oracle, SQL Server, MySQL, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86b20d935fd5092a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c6d2549522637c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6ea25bee3a2f193</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe0d78f48801be2</t>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58e8526e088cb1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Metadata Specialist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tekraft Corporation</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Kafka, PostgreSQL, MongoDB, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998f2d65c888a408</t>
+          <t>https://www.indeed.com/viewjob?jk=e43efa70b96122a9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef39faa18331e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bf762c4708388f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e12c51d5852d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b49e29b8a554ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604b79461fedf927</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97fe63b06d0368a</t>
+          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Project - Data Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lexington, SC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39165c25f32dbb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abfcf8fd5fce3258</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0e0f9ecf7f9e54</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f475ba0fa29d4a2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13fb4ea225ed1fcf</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a764a06d81d641a</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=823e9e92cfcbb982</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1443315787438a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868ea3e4e3bd4a8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3763ac0aaf5fe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Project - Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, ELT</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d30b799c1e5b8a40</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Data Engineer, CX</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=602641e1ce530091</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>MDM Architect</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>redan</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>GenAI Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Gen AI Sr. Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0e218931bd7dc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Convoy of Hope</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Backend Engineer _ AI Gateway</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Woongjin, Inc</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Backend Engineer_AI Gateway</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Sbt Global</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>The Weather Company</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Andover, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34cf04c12e423597</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>The Washington Post</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Lambda, Step Functions, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, Splunk, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9aec2a1b87419d</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Python, Databricks</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Vistar Media</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Peterson Caterpillar</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>San Leandro, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Objectways Technologies</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>eLinx Health, LLC</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Middle Data Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Itransition</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>BigQuery, Snowflake, Oracle, SQL Server, MySQL, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c6d2549522637c</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Press Ganey</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Provo, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Delinea</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Junior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Trellance</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Metadata Specialist</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Tekraft Corporation</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Kafka, PostgreSQL, MongoDB, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e43efa70b96122a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Full Stack AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Freedom Mortgage</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Marlton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Redmond, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Lexington, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Data Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Backend Engineer- Hybrid</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Backend Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
+          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Reliability Developer</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Arctic Wolf Networks</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb9a8bc7b5038ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>Senior Reliability Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>Arctic Wolf Networks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb9a8bc7b5038ad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ClosingLock</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior GCP CloudOps Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Azure Full Stack Developer</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Platform Architect, Strategy and Enablement</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>ClosingLock</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior GCP CloudOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
+          <t>Senior Azure Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
+          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SrinSoft Technologies</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>US LBM AI Engineer</t>
+          <t>AI Platform Architect, Strategy and Enablement</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
+          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer L3</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SQL Server</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>SrinSoft Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Weston, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>US LBM AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
+          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Professional Services)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Software Engineer L3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
+          <t>Solutions Architect - Financial Services</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
+          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Solutions Architect - Financial Services (Professional Services)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,59 +3646,59 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
+          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cba82380663ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lambda, Step Functions, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, Splunk, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9aec2a1b87419d</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
+          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vistar Media</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
+          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Software Engineer III (Java/Spring)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Peterson Caterpillar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>eLinx Health, LLC</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Middle Data Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Itransition</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>BigQuery, Snowflake, Oracle, SQL Server, MySQL, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c6d2549522637c</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>Lambda, Step Functions, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, Splunk, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9aec2a1b87419d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Metadata Specialist</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tekraft Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Kafka, PostgreSQL, MongoDB, Git, CloudWatch</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43efa70b96122a9</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>eLinx Health, LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Middle Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Itransition</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>BigQuery, Snowflake, Oracle, SQL Server, MySQL, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c6d2549522637c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lexington, SC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,17 +4581,332 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Junior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Trellance</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Metadata Specialist</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tekraft Corporation</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Kafka, PostgreSQL, MongoDB, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e43efa70b96122a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Lexington, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
+          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Software Backend Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Backend Engineer- Hybrid</t>
+          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Azure Full Stack Developer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Senior Azure Full Stack Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
         </is>
       </c>
     </row>
@@ -2486,29 +2486,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SrinSoft Technologies</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>US LBM AI Engineer</t>
+          <t>SQL Server</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>SrinSoft Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Weston, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
+          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>US LBM AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer L3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer L3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Professional Services)</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect - Financial Services</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Solutions Architect - Financial Services (Professional Services)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
+          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
+          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
+          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Informatica MDM Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
+          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring)</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer III (Java/Spring)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,19 +4206,19 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lambda, Step Functions, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, Splunk, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,59 +4311,59 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9aec2a1b87419d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vistar Media</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Peterson Caterpillar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>eLinx Health, LLC</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Middle Data Engineer</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Itransition</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>BigQuery, Snowflake, Oracle, SQL Server, MySQL, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c6d2549522637c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>eLinx Health, LLC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Middle Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Itransition</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>BigQuery, Snowflake, Oracle, SQL Server, MySQL, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c6d2549522637c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Metadata Specialist</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tekraft Corporation</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Kafka, PostgreSQL, MongoDB, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43efa70b96122a9</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Full-Stack Developer, Senior</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Technica Corporation</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2907628bc43ed13</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Lexington, SC, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,15 +4896,85 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Lexington, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS ETL Data Engineer - HYBRID</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f3b0a20014410c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
+          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
+          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Databricks Architect - (ADLS, S3, or GCS).</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
+          <t>https://www.indeed.com/viewjob?jk=066f34528bcf8419</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Architect - (ADLS, S3, or GCS).</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066f34528bcf8419</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Azure Data Engineer with Elasticsearch Experience</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Elasticsearch Experience</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
         </is>
       </c>
     </row>
@@ -1483,52 +1483,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
+          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
+          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Reliability Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Arctic Wolf Networks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
+          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Reliability Developer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Arctic Wolf Networks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
+          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
+          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>GCP Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1882,38 +1882,38 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb9a8bc7b5038ad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb9a8bc7b5038ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>ClosingLock</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior GCP CloudOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ClosingLock</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior GCP CloudOps Engineer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Senior Azure Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Azure Full Stack Developer</t>
+          <t>AI Platform Architect, Strategy and Enablement</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
+          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Platform Architect, Strategy and Enablement</t>
+          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
+          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
@@ -2486,29 +2486,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
+          <t>SQL Server</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>SrinSoft Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Weston, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
+          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>US LBM AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SrinSoft Technologies</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>US LBM AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer L3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer L3</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Solutions Architect - Financial Services</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
+          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Solutions Architect - Financial Services (Professional Services)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
+          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Professional Services)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
+          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
+          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Informatica MDM Architect</t>
+          <t>Software Engineer III (Java/Spring)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring)</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,104 +4266,104 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vistar Media</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Peterson Caterpillar</t>
+          <t>eLinx Health, LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
+          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>eLinx Health, LLC</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Middle Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Itransition</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>BigQuery, Snowflake, Oracle, SQL Server, MySQL, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c6d2549522637c</t>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>Full-Stack Developer, Senior</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Technica Corporation</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=e2907628bc43ed13</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Full-Stack Developer, Senior</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Technica Corporation</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2907628bc43ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
+          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lexington, SC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4870,111 +4870,6 @@
         </is>
       </c>
       <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Lexington, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hagerty</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, ECS, RDS, Azure, GCP, HDFS, MapReduce</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Databricks, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f6e1bedc5aca93</t>
+          <t>https://www.indeed.com/viewjob?jk=7de6f50bed06cb2e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Databricks, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002cb1d712286720</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6ed1b6bcf72320</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Databricks, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de6f50bed06cb2e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f13002e35d6260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Databricks, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6ed1b6bcf72320</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0d12975625b7b9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Engineer - East Coast</t>
+          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3467fd4232b4427</t>
+          <t>https://www.indeed.com/viewjob?jk=e80f5516efca193f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f13002e35d6260</t>
+          <t>https://www.indeed.com/viewjob?jk=0528c489587de6f9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0d12975625b7b9</t>
+          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>Data Engineer II - General Motors Insurance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80f5516efca193f</t>
+          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0528c489587de6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea27190f32e93ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II - General Motors Insurance</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
+          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
+          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
+          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Azure Data Engineer with Elasticsearch Experience</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Architect - (ADLS, S3, or GCS).</t>
+          <t>Software Backend Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=066f34528bcf8419</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Elasticsearch Experience</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Backend Engineer- Hybrid</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Reliability Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Arctic Wolf Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
+          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Reliability Developer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Arctic Wolf Networks</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
+          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
+          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCP Data Engineer/Architect</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebb9a8bc7b5038ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>ClosingLock</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Senior GCP CloudOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Azure Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>AI Platform Architect, Strategy and Enablement</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ClosingLock</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior GCP CloudOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Azure Full Stack Developer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Platform Architect, Strategy and Enablement</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
+          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SQL Server</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>SrinSoft Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Weston, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer L3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
+          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
+          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SrinSoft Technologies</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>US LBM AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
+          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer L3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
         </is>
       </c>
     </row>
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Early Career: IT Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c8e81b9cc71fac</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c365cd2854a53060</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Professional Services)</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ec1e1b2bf91dc9</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
+          <t>Software Engineer III (Java/Spring)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
+          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
+          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,77 +3951,77 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Informatica MDM Architect</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring)</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4052,11 +4052,11 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
+          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,59 +4241,59 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>Full-Stack Developer, Senior</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Technica Corporation</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2907628bc43ed13</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
+          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vistar Media</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
+          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
+          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Peterson Caterpillar</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Healthcare IT Integration Engineer (OpenEMR &amp; Clearinghouse)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>eLinx Health, LLC</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f404d30d421a652a</t>
+          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Lexington, SC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4555,321 +4555,6 @@
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Delinea</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Junior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Trellance</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Full-Stack Developer, Senior</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Technica Corporation</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2907628bc43ed13</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Full Stack AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Freedom Mortgage</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Marlton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Lexington, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Java Developer - Child Support Management System</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,77 +486,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Databricks, Medallion Architecture, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de6f50bed06cb2e</t>
+          <t>https://www.indeed.com/viewjob?jk=817df956fbf694bd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, Databricks, Medallion Architecture, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6ed1b6bcf72320</t>
+          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f13002e35d6260</t>
+          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>Data Engineer II - General Motors Insurance</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0d12975625b7b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80f5516efca193f</t>
+          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied AI Site Reliability Engineer III - PxE Talent</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0528c489587de6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II - General Motors Insurance</t>
+          <t>Senior DotNET Developer - Child Support Management System</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
+          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
+          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
+          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Data Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
+          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Elasticsearch Experience</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Software Engineers</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Backend Engineer- Hybrid</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7ea8491fb4bdff</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
+          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
+          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior ML Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,46 +1532,46 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
+          <t>https://www.indeed.com/viewjob?jk=342724222b8446f4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Reliability Developer</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Arctic Wolf Networks</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5af11f0f64610c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Azure Full Stack Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
+          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Azure Cosmos DB, ELT, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,137 +1791,137 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineering Advisor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=78f82eb1c3ef3a0b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>Sr. Developer - Automation Core</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ClosingLock</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3d3173f400d1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior GCP CloudOps Engineer</t>
+          <t>SQL Server</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>SrinSoft Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Weston, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Azure Full Stack Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
+          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Platform Architect, Strategy and Enablement</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
+          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SAP PS/PPM Functional Consultant (Microsoft)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbaac0f5c3a6c90a</t>
+          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
         </is>
       </c>
     </row>
@@ -2188,20 +2188,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, ETL, ELT, Power BI, DataOps</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack - Software Engineer II (Power Distribution Equipment, Utility, HMI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc026a652edd019</t>
+          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SrinSoft Technologies</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer L3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer L3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP S/4HANA MMPP Functional Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>ClassWallet</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Early Career: IT Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Early Career: IT Security Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>BambooHR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
+          <t>https://www.indeed.com/viewjob?jk=1aeae119ed68b4e0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
+          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GCP BigQuery+Nifi+Kafa Data Engineer</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e2874b216a47f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
+          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
+          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Informatica MDM Architect</t>
+          <t>Software Engineer III (Java/Spring)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,49 +3681,49 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
+          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0510f5b12bfd66b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring)</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,59 +3926,59 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vistar Media</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Peterson Caterpillar</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
+          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Lexington, SC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4275,286 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Full-Stack Developer, Senior</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Technica Corporation</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2907628bc43ed13</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Full Stack AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Freedom Mortgage</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Marlton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Redmond, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Lexington, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
+          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Engineer II - General Motors Insurance</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II - General Motors Insurance</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
+          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
+          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
         </is>
       </c>
     </row>
@@ -748,35 +748,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
+          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Loffler Companies, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d931b69fdd57a33</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineers</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie, Flume</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766da569703272f</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
+          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
+          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior ML Data Engineer</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342724222b8446f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,94 +1616,94 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Azure Full Stack Developer</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8622a181db01697f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Sr. Developer - Automation Core</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,209 +1781,209 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f82eb1c3ef3a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Developer - Automation Core</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Clarksburg, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ClassWallet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SQL Server</t>
+          <t>Early Career: IT Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SrinSoft Technologies</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Weston, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474940d0db2dbb02</t>
+          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>SAP S/4HANA MMPP Functional Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,77 +2271,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer L3</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Spark, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SAP S/4HANA MMPP Functional Consultant</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ClassWallet</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Early Career: IT Security Engineer</t>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3345dd413dc8727</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,137 +3086,137 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BambooHR</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Lexington, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aeae119ed68b4e0</t>
+          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3260,1021 +3260,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Engineer, CX</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Data Engineer, CX</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Kore.ai</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>accrete</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Moody's</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Informatica MDM Architect</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Convoy of Hope</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Backend Engineer _ AI Gateway</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Woongjin, Inc</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Backend Engineer_AI Gateway</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Sbt Global</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Operations Specialist (DBA) US CITIZENS ONLY</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>redan</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Snowflake, SQL Server, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e61ffe9035451db</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Python Software Engineer - Financial Engineering</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Risk Analytics</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Guilford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Engineer III (Java/Spring)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Splunk, CI/CD, Maven, Terraform</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b55f92b3368913f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Nationwide Mutual Insurance Company</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Python, Databricks</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Vistar Media</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Peterson Caterpillar</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>San Leandro, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Objectways Technologies</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3bd98be19932593</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Cardiff</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>State Street</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Quincy, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Press Ganey</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Provo, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>UI Developer - Guest Commerce &amp; Distribution - C1</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>S3, IAM, RDS, Azure, Scala, MySQL, CI/CD, Azure DevOps, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3630239785d032c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Delinea</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Full Stack AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Freedom Mortgage</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Marlton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Redmond, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Lexington, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Junior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Trellance</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Breeze Airways</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Java Developer - Child Support Management System</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,112 +496,112 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817df956fbf694bd</t>
+          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior Java Developer - Child Support Management System</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=817df956fbf694bd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II - General Motors Insurance</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
+          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Technical Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Sparksoft Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb08bdb737e91628</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
+          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer II - General Motors Insurance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
+          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DotNET Developer - Child Support Management System</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,322 +731,322 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f89500c8c96cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Senior DotNET Developer - Child Support Management System</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
+          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loffler Companies, Inc.</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
+          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Loffler Companies, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
+          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Microsoft Certified Power Platform Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>j. anukem &amp; associates</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=9829e7244bb5e65a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MongoDB, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,151 +1392,151 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>Business Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Developer - Automation Core</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Clarksburg, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10beb430d349bbba</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Developer - Automation Core</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ClassWallet</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Early Career: IT Security Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAP S/4HANA MMPP Functional Consultant</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
+          <t>https://www.indeed.com/viewjob?jk=40e0ca68ce74674c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>ClassWallet</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Cloud SME X2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>SAP S/4HANA MMPP Functional Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,199 +2421,199 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Informatica MDM Architect</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Early Career: IT Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,77 +2691,77 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,172 +2771,172 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vistar Media</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Spark, Scala, Kafka, ETL, DataOps, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=0c55d5a480e1ba95</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Peterson Caterpillar</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Azure Cosmos DB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee2a8d1b8adb9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lexington, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da359f17a501a2a8</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, Snowflake, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Software Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,155 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>State Street</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Quincy, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Smarty</t>
+          <t>Dutch Bros Coffee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd616fb4621cbc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Java Developer - Child Support Management System</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Smarty</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SNS, ECS, IAM, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817df956fbf694bd</t>
+          <t>https://www.indeed.com/viewjob?jk=232fc1791e50c6b0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Java Developer - Child Support Management System</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
+          <t>https://www.indeed.com/viewjob?jk=817df956fbf694bd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technical Solution Architect</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sparksoft Corporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>IAM, RDS, Medallion Architecture, GCP, BigQuery, Dataflow, Vertex AI, Hadoop, Hive, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb08bdb737e91628</t>
+          <t>https://www.indeed.com/viewjob?jk=751ce7cf6c298548</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Technical Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>Sparksoft Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb08bdb737e91628</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II - General Motors Insurance</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
+          <t>https://www.indeed.com/viewjob?jk=19d05ad83816aaf7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Engineer II - General Motors Insurance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
+          <t>https://www.indeed.com/viewjob?jk=5080f9a281fb787e</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
+          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
+          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DotNET Developer - Child Support Management System</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DotNET Developer - Child Support Management System</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
+          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Loffler Companies, Inc.</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,87 +1116,87 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Loffler Companies, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Microsoft Certified Power Platform Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>j. anukem &amp; associates</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9829e7244bb5e65a</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Microsoft Certified Power Platform Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>j. anukem &amp; associates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
+          <t>https://www.indeed.com/viewjob?jk=9829e7244bb5e65a</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,94 +1406,94 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Data Architect</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Business Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Developer - Automation Core</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Information and Referral Federation of Los Angeles County</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e0ca68ce74674c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Developer - Automation Core</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ClassWallet</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud SME X2</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SAP S/4HANA MMPP Functional Consultant</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Cloud SME X2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7570321d97679526</t>
+          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>SAP S/4HANA MMPP Functional Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>ClassWallet</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Early Career: IT Security Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,94 +2596,94 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=536a5cbcba65868f</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c55d5a480e1ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Informatica MDM Architect</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c55d5a480e1ba95</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,77 +3041,77 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Kafka, Oracle, SQL Server, MongoDB, NoSQL, ETL</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Engineer — GTM Analytics</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Software Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+          <t>Senior Software Engineer (Remote) - Radiology</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Software Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,332 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>State Street</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Quincy, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Breeze Airways</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=642a2e2441a31d20</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4555ba9a9f5693be</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94a8a92e1381b54a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2413e7f250d00cb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e1faeaec512b702</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-30.xlsx
+++ b/results/job_matches_2026-07-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38e19e4e49ff838f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, IAM, RDS, Azure, Databricks, GCP, Hive</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2b990b655e9f01</t>
+          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DotNET Developer - Child Support Management System</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, ECS</t>
+          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bc1c0882246fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, DataOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be67238d1b6a44a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Premier Nutrition Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d49984ac43ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DotNET Developer - Child Support Management System</t>
+          <t>Senior Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1474978de0278b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Software Engineer I / II — AWS &amp; .NET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e610a35113b8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Premier Nutrition Company</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0802dcc649446c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer</t>
+          <t>Software Engineer III - AWS, Databricks, Python</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8279b19004b6546d</t>
+          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer I / II — AWS &amp; .NET</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Young Living Essential Oils</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced6761489507437</t>
+          <t>https://www.indeed.com/viewjob?jk=735136a340f06328</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data and Analytics AI Engineer</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Loffler Companies, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4077f69e7bd948e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS, Databricks, Python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Museum of Modern Art</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118a88261f4a95ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Power BI Data Analyst</t>
+          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Loffler Companies, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, Scala, SQL Server, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d521ef740f60ce71</t>
+          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Microsoft Certified Power Platform Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Museum of Modern Art</t>
+          <t>j. anukem &amp; associates</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcc4b2fa6c73536</t>
+          <t>https://www.indeed.com/viewjob?jk=9829e7244bb5e65a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Spark &amp; ETL) (contract)</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6850350b918febb4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
+          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
+          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Certified Power Platform Solution Architect</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>j. anukem &amp; associates</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,129 +1371,129 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9829e7244bb5e65a</t>
+          <t>https://www.indeed.com/viewjob?jk=f01a424e09b95ee6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Data Engineer - Onboarding</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sardine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0880f7398d068d</t>
+          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Business Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295ba1b258eef725</t>
+          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5649f49af7e717e1</t>
+          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - Onboarding</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sardine</t>
+          <t>Caltrans - CA Dept. of Transportation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, dbt, CI/CD</t>
+          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafe0da0cb06f132</t>
+          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Business Data Architect</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Spark Streaming</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd28b1da9cfe4d40</t>
+          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Engineer, AI Strategy and Solutions</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Universal Creative</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235882076ff46707</t>
+          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>AI, AWS DevOps, Java/Python Software Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caltrans - CA Dept. of Transportation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Data Factory, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804ad5c43a97ea75</t>
+          <t>https://www.indeed.com/viewjob?jk=65068caf46548141</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a004e42eab6632</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer, AI Strategy and Solutions</t>
+          <t>Senior AI/ML Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Universal Creative</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6766b0436a9e52df</t>
+          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Senior Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8c3d75cc5a59c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI/ML Data Engineer</t>
+          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,29 +1746,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7493eab3654bd62</t>
+          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer</t>
+          <t>Consulting Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,73 +1777,73 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7133d5b08431c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (SMTS), Identity &amp; Access Management - Device Trust</t>
+          <t>Cloud Engineer Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd560d3519b576ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Consulting Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Berkshire Hathaway GUARD Insurance Companies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff47d92a692d4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Engineer Senior</t>
+          <t>Senior Data Transformation Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Patriot Bank, N.A.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, API Gateway, IAM, RDS, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca6f5d8776368811</t>
+          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst (Hybrid - Madison or Austin)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway GUARD Insurance Companies</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d44e48661eb7c09</t>
+          <t>https://www.indeed.com/viewjob?jk=289d005fb52fdb68</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Developer - Automation Core</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Information and Referral Federation of Los Angeles County</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, Dimensional Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=395dca48176f846b</t>
+          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
+          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Transformation Data Architect</t>
+          <t>Sr Dir Software - Data Platform Engineer - Minneapolis, MN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Patriot Bank, N.A.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7777dc92cdf89b5a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8fa88f7e3fd0c2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Developer - Automation Core</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e334c03bdbb374</t>
+          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Architect/Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, Blob Storage, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116af8cbccb591b5</t>
+          <t>https://www.indeed.com/viewjob?jk=70a69ee2362e8f4b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Domo, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f5da6a90e11da1</t>
+          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MIAX</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hadoop, HDFS, YARN, Spark, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Domo, Inc.</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c47bac900059df12</t>
+          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Engineer (Remote)</t>
+          <t>Sr Associate Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2b8d579584394d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Senior BI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Daisy Brand</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854756df3635191</t>
+          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer, IT Software</t>
+          <t>Cloud SME X2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f18b9877a4bf7ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior BI Engineer</t>
+          <t>SAP S/4HANA MMPP Functional Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Daisy Brand</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b1714cc80b634c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud SME X2</t>
+          <t>Advanced Specialist, Software Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Juno Beach, FL, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a558c1d3bd32ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAP S/4HANA MMPP Functional Consultant</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>ClassWallet</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b51f21983ae125e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Software Engineering</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5038ceada916f64</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ClassWallet</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5859053628eb5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software Dev Test Quality Engineering (Req# 000106)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, RDS, Cloud Storage, Kafka, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5094515b70d2d99</t>
+          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI Foundational Model Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1820a549077871</t>
+          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Senior Engineer, Data and AI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Cisive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,94 +2596,94 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40978ef369a5ee61</t>
+          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer - ML Infrastructure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Epsilon Labs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9708ccf9ee0f5af2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Foundational Model Engineer</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=376d725617b0f2aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data and AI</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cisive</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, NoSQL, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743af78e2a52e54b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - ML Infrastructure</t>
+          <t>Data Engineer, CX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Epsilon Labs</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, MLOps, Docker</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b12d9efc6c6a98</t>
+          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff73ed78b417b14</t>
+          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Data Engineer-Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e1bb5d1e28bb584</t>
+          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ff52dcf36f3231</t>
+          <t>https://www.indeed.com/viewjob?jk=0c55d5a480e1ba95</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, CX</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b965f75c7a3a4cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer-Data Platform &amp; Analytics</t>
+          <t>Informatica MDM Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b950c881dbe97c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Convoy of Hope</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c55d5a480e1ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bd0abe4afa5b39</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Informatica MDM Architect</t>
+          <t>Python Software Engineer - Financial Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Risk Analytics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Guilford, CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,182 +3006,182 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b228bf7b8568d089</t>
+          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Integrations Engineer I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Convoy of Hope</t>
+          <t>Kendra Scott</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, REST API integration</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2fab49ef78904e1</t>
+          <t>https://www.indeed.com/viewjob?jk=58b78bbfcdcc6779</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway</t>
+          <t>Specialist, Data Engineer - SQL and Snowflake</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
+          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend Engineer_AI Gateway</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Reach Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
+          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer - Palantir Foundry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, Snowflake, DynamoDB</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d0534e87a93a57</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Financial Engineering</t>
+          <t>Senior Software Engineer (Remote) - Radiology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Risk Analytics</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Guilford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d644129f935bd266</t>
+          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer - SQL and Snowflake</t>
+          <t>AI Engineer — GTM Analytics</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c79cad4a6a280f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Software Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Reach Financial</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62588f4999e63221</t>
+          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Palantir Foundry</t>
+          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ca9632878562c</t>
+          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Remote) - Radiology</t>
+          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Washington University in St. Louis</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e445dc5779186f6</t>
+          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI Engineer — GTM Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Breeze Airways</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Databricks Lakehouse, ELT, dbt, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9697dd941d556f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Software Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, MLOps, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5333ce5a9b1f0a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=642a2e2441a31d20</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Python Engineer, Financial Data Platform &amp; Integrations</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, Snowflake, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44c5ea64ad488307</t>
+          <t>https://www.indeed.com/viewjob?jk=4555ba9a9f5693be</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Encryption Engineer (DevSecOps &amp; SDLC)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143efb56cf174073</t>
+          <t>https://www.indeed.com/viewjob?jk=94a8a92e1381b54a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
+          <t>https://www.indeed.com/viewjob?jk=2413e7f250d00cb8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Breeze Airways</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,190 +3531,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6733d266b961b</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=642a2e2441a31d20</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4555ba9a9f5693be</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94a8a92e1381b54a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2413e7f250d00cb8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Spark, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1e1faeaec512b702</t>
         </is>
